--- a/outputs/etf_trend_strategy/threshold_0.7/backtests/window_40/return_r2/post_rank_positive_return/rebalance_1d/next_day_vwap/next_day_vwap_annual_metrics.xlsx
+++ b/outputs/etf_trend_strategy/threshold_0.7/backtests/window_40/return_r2/post_rank_positive_return/rebalance_1d/next_day_vwap/next_day_vwap_annual_metrics.xlsx
@@ -469,9 +469,9 @@
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -524,25 +524,25 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>-0.00834617080900224</v>
+        <v>-0.1181002249878126</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.3427409376523726</v>
+        <v>0.1982791837008102</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>0.09986967305614225</v>
+        <v>-0.6920426246321743</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.1404165168733806</v>
+        <v>-0.9188711221165786</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.2347200346811867</v>
+        <v>0.2160363687544028</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>-0.04016025503974748</v>
+        <v>-0.6128436737642283</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>36.38420853099066</v>
+        <v>37.13593009287603</v>
       </c>
     </row>
     <row r="3">
@@ -552,25 +552,25 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-0.2369012787331027</v>
+        <v>-0.06459082135597571</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.2613345254053865</v>
+        <v>0.2874464789314894</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>-1.003324795020895</v>
+        <v>-0.1507482455865936</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-1.352316462410517</v>
+        <v>-0.215804107286471</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.3148283287025475</v>
+        <v>0.1929275813329785</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-0.7794068073508114</v>
+        <v>-0.3481523469008532</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>46.82721876254479</v>
+        <v>20.8119221771995</v>
       </c>
     </row>
     <row r="4">
@@ -580,25 +580,25 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0.003803671755061133</v>
+        <v>-0.07363264575946327</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.2321918890026882</v>
+        <v>0.2287335535852025</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>0.06825250109715023</v>
+        <v>-0.2989985658126205</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.1005638392831772</v>
+        <v>-0.4075080671933415</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.2119862263370857</v>
+        <v>0.2919897193272849</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0.01868592710398791</v>
+        <v>-0.2621866965393999</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>41.31133775346392</v>
+        <v>46.86612479855332</v>
       </c>
     </row>
     <row r="5">
@@ -608,25 +608,25 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>-0.066098719973543</v>
+        <v>0.1697160814752787</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0.2319440446343066</v>
+        <v>0.3132554249043439</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>-0.2560902474329421</v>
+        <v>0.6278578200110286</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>-0.3733750822885658</v>
+        <v>0.9939152494435697</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.2449815171110759</v>
+        <v>0.2190244963692954</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-0.2805681868373831</v>
+        <v>0.8095796729478327</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>44.17346219807251</v>
+        <v>37.97403614804998</v>
       </c>
     </row>
     <row r="6">
@@ -636,25 +636,25 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.2124295300379513</v>
+        <v>0.360988492513026</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0.2756398272512746</v>
+        <v>0.3156545642389595</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.809371412922654</v>
+        <v>1.123788703782118</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1.1216773236875</v>
+        <v>1.62784602621853</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.2605292746380578</v>
+        <v>0.2407068391979373</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.8486965645443986</v>
+        <v>1.564614887056267</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>53.18638923196603</v>
+        <v>41.66481831419578</v>
       </c>
     </row>
     <row r="7">
@@ -664,25 +664,25 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.03121587787724733</v>
+        <v>0.3803558300605538</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.3392435990901961</v>
+        <v>0.4150234653033796</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.2894038226326403</v>
+        <v>1.578705265142475</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.4059115953767982</v>
+        <v>2.48588594961897</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.2467948820349178</v>
+        <v>0.1713938175523225</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.2322151310601018</v>
+        <v>4.631986259109225</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>31.22181326863961</v>
+        <v>37.4508841569935</v>
       </c>
     </row>
   </sheetData>
